--- a/tests/Testing.xlsx
+++ b/tests/Testing.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4c7d7d98c037d19b/Level 6/Cloud/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4c7d7d98c037d19b/Level 6/Cloud/ACDT CW2 Updated/tests/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="82" documentId="8_{AB4D71AA-F82A-4017-8E7A-B8E1FF7AC13D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F89F414D-ECF2-492D-AAA2-A975A2D08059}"/>
+  <xr:revisionPtr revIDLastSave="112" documentId="8_{AB4D71AA-F82A-4017-8E7A-B8E1FF7AC13D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EB2213FE-3847-47D3-9F2D-26636208F9B4}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{0FD93C22-EA38-4C55-8FBA-9A662F17215C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{0FD93C22-EA38-4C55-8FBA-9A662F17215C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -152,18 +152,6 @@
     <t>test_correlation_id_for_is_deterministic_and_12_chars</t>
   </si>
   <si>
-    <t>test_extract_source_domain_from_url</t>
-  </si>
-  <si>
-    <t>test_extract_source_domain_from_text_domain</t>
-  </si>
-  <si>
-    <t>test_extract_source_domain_returns_none_when_missing_name</t>
-  </si>
-  <si>
-    <t>test_extract_source_domain_bad_url_returns_none</t>
-  </si>
-  <si>
     <t>test_read_emails_from_csv_strips_and_keeps_order</t>
   </si>
   <si>
@@ -218,12 +206,6 @@
     <t>Verify CID consistency and length</t>
   </si>
   <si>
-    <t>Extract domain from URL</t>
-  </si>
-  <si>
-    <t>Extract domain from free text</t>
-  </si>
-  <si>
     <t>Handle missing name field</t>
   </si>
   <si>
@@ -281,9 +263,6 @@
     <t>URL with subdomain</t>
   </si>
   <si>
-    <t>Text containing domain</t>
-  </si>
-  <si>
     <t>Empty name</t>
   </si>
   <si>
@@ -347,9 +326,6 @@
     <t>Hashing</t>
   </si>
   <si>
-    <t>Domain Extraction</t>
-  </si>
-  <si>
     <t>Analyst Summary</t>
   </si>
   <si>
@@ -861,7 +837,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>tests/test_main.py::test_extract_source_domain_from_url</t>
+      <t>tests/test_main.py::test_read_emails_from_csv_strips_and_keeps_order</t>
     </r>
     <r>
       <rPr>
@@ -892,6 +868,372 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
+      <t xml:space="preserve">  </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>tests/test_main.py::test_screen_email_polls_until_records_found</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PASSED</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">    </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>tests/test_main.py::test_request_does_not_retry_on_non_retry_status</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PASSED</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>tests/test_main.py::test_request_honours_retry_after_header</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PASSED</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>tests/test_main.py::test_build_analyst_summary_counts_and_top_sources</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PASSED</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>tests/test_main.py::test_write_summary_csv_writes_expected_layout</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PASSED</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">   </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">tests/test_main.py::test_write_breach_chart_png_creates_file_when_breaches_exist </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PASSED</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>tests/test_main.py::test_write_breach_chart_png_skips_when_no_breaches</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PASSED</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <t>Source Extraction</t>
+  </si>
+  <si>
+    <t>Extract source from URL</t>
+  </si>
+  <si>
+    <t>Extract source from free text</t>
+  </si>
+  <si>
+    <t>Text containing source</t>
+  </si>
+  <si>
+    <t>test_extract_source_from_url</t>
+  </si>
+  <si>
+    <t>test_extract_source_from_text</t>
+  </si>
+  <si>
+    <t>test_extract_source_returns_none_when_missing_name</t>
+  </si>
+  <si>
+    <t>test_extract_source_bad_url_returns_none</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>tests/test_main.py::test_extract_domain_from_url</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PASSED</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">       </t>
     </r>
   </si>
@@ -905,7 +1247,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>tests/test_main.py::test_extract_source_domain_from_text_domain</t>
+      <t>tests/test_main.py::test_extract_source_from_text</t>
     </r>
     <r>
       <rPr>
@@ -949,7 +1291,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>tests/test_main.py::test_extract_source_domain_returns_none_when_missing_name</t>
+      <t>tests/test_main.py::test_extract_source_returns_none_when_missing_name</t>
     </r>
     <r>
       <rPr>
@@ -993,7 +1335,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">tests/test_main.py::test_extract_source_domain_bad_url_returns_none </t>
+      <t xml:space="preserve">tests/test_main.py::test_extract_source_bad_url_returns_none </t>
     </r>
     <r>
       <rPr>
@@ -1015,348 +1357,6 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">   </t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>tests/test_main.py::test_read_emails_from_csv_strips_and_keeps_order</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF00B050"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>PASSED</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">  </t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>tests/test_main.py::test_screen_email_polls_until_records_found</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF00B050"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>PASSED</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">    </t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>tests/test_main.py::test_request_does_not_retry_on_non_retry_status</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF00B050"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>PASSED</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>tests/test_main.py::test_request_honours_retry_after_header</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF00B050"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>PASSED</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">  </t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>tests/test_main.py::test_build_analyst_summary_counts_and_top_sources</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF00B050"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>PASSED</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">  </t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>tests/test_main.py::test_write_summary_csv_writes_expected_layout</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF00B050"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>PASSED</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">   </t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">tests/test_main.py::test_write_breach_chart_png_creates_file_when_breaches_exist </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF00B050"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>PASSED</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">  </t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>tests/test_main.py::test_write_breach_chart_png_skips_when_no_breaches</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF00B050"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>PASSED</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
     </r>
   </si>
 </sst>
@@ -1486,20 +1486,20 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>27</xdr:row>
-      <xdr:rowOff>9525</xdr:rowOff>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>1487853</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>19663</xdr:rowOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>3298167</xdr:colOff>
+      <xdr:row>49</xdr:row>
+      <xdr:rowOff>162533</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="18" name="Picture 17">
+        <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4A75BD18-A0C5-F003-BAEE-CDE521BA8618}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{58C4BEC0-A8AD-8244-2FDB-36038662FAB9}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1515,8 +1515,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="5153025"/>
-          <a:ext cx="13994178" cy="4391638"/>
+          <a:off x="0" y="5143500"/>
+          <a:ext cx="18033342" cy="4353533"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1878,13 +1878,13 @@
         <v>6</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
       <c r="I1" s="6" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
@@ -1902,22 +1902,22 @@
         <v>2</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="E3" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="F3" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="G3" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="I3" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
@@ -1931,22 +1931,22 @@
         <v>2</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="E4" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="F4" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="G4" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="I4" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
@@ -1957,25 +1957,25 @@
         <v>30</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="D5" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E5" t="s">
         <v>48</v>
       </c>
-      <c r="E5" t="s">
-        <v>52</v>
-      </c>
       <c r="F5" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="G5" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="I5" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
@@ -1986,25 +1986,25 @@
         <v>31</v>
       </c>
       <c r="C6" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="E6" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="F6" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="G6" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="I6" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
@@ -2015,25 +2015,25 @@
         <v>32</v>
       </c>
       <c r="C7" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="E7" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="F7" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="G7" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="I7" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
@@ -2044,25 +2044,25 @@
         <v>33</v>
       </c>
       <c r="C8" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="E8" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="F8" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="G8" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="I8" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
@@ -2073,25 +2073,25 @@
         <v>34</v>
       </c>
       <c r="C9" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="E9" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="F9" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="G9" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="I9" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
@@ -2102,25 +2102,25 @@
         <v>35</v>
       </c>
       <c r="C10" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="E10" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="F10" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="G10" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="I10" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
@@ -2131,25 +2131,25 @@
         <v>36</v>
       </c>
       <c r="C11" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="E11" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="F11" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="G11" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="I11" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
@@ -2160,25 +2160,25 @@
         <v>37</v>
       </c>
       <c r="C12" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="E12" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="F12" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="G12" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="I12" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
@@ -2186,28 +2186,28 @@
         <v>18</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>38</v>
+        <v>132</v>
       </c>
       <c r="C13" t="s">
-        <v>103</v>
+        <v>128</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="E13" t="s">
-        <v>60</v>
+        <v>129</v>
       </c>
       <c r="F13" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="G13" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="I13" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
@@ -2215,28 +2215,28 @@
         <v>19</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>39</v>
+        <v>133</v>
       </c>
       <c r="C14" t="s">
-        <v>103</v>
+        <v>128</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="E14" t="s">
-        <v>61</v>
+        <v>130</v>
       </c>
       <c r="F14" t="s">
-        <v>81</v>
+        <v>131</v>
       </c>
       <c r="G14" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="I14" t="s">
-        <v>129</v>
+        <v>137</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
@@ -2244,28 +2244,28 @@
         <v>20</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>40</v>
+        <v>134</v>
       </c>
       <c r="C15" t="s">
-        <v>103</v>
+        <v>128</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="E15" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="F15" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="G15" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="H15" s="5" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="I15" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
@@ -2273,28 +2273,28 @@
         <v>21</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>41</v>
+        <v>135</v>
       </c>
       <c r="C16" t="s">
-        <v>103</v>
+        <v>128</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="E16" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="F16" t="s">
+        <v>76</v>
+      </c>
+      <c r="G16" t="s">
         <v>83</v>
       </c>
-      <c r="G16" t="s">
-        <v>90</v>
-      </c>
       <c r="H16" s="5" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="I16" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
@@ -2302,28 +2302,28 @@
         <v>22</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="C17" t="s">
         <v>2</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="E17" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="F17" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="G17" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="I17" t="s">
-        <v>132</v>
+        <v>120</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
@@ -2331,28 +2331,28 @@
         <v>23</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="C18" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="E18" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="F18" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="G18" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="H18" s="5" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="I18" t="s">
-        <v>133</v>
+        <v>121</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
@@ -2360,28 +2360,28 @@
         <v>24</v>
       </c>
       <c r="B19" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C19" t="s">
+        <v>93</v>
+      </c>
+      <c r="D19" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C19" t="s">
-        <v>100</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>48</v>
-      </c>
       <c r="E19" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="F19" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="G19" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="H19" s="5" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="I19" t="s">
-        <v>134</v>
+        <v>122</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
@@ -2389,28 +2389,28 @@
         <v>25</v>
       </c>
       <c r="B20" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="C20" t="s">
+        <v>93</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E20" t="s">
+        <v>61</v>
+      </c>
+      <c r="F20" t="s">
+        <v>80</v>
+      </c>
+      <c r="G20" t="s">
+        <v>83</v>
+      </c>
+      <c r="H20" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="C20" t="s">
-        <v>100</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="E20" t="s">
-        <v>67</v>
-      </c>
-      <c r="F20" t="s">
-        <v>87</v>
-      </c>
-      <c r="G20" t="s">
-        <v>90</v>
-      </c>
-      <c r="H20" s="5" t="s">
-        <v>49</v>
-      </c>
       <c r="I20" t="s">
-        <v>135</v>
+        <v>123</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
@@ -2418,28 +2418,28 @@
         <v>26</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C21" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="E21" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="F21" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="G21" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="H21" s="5" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="I21" t="s">
-        <v>136</v>
+        <v>124</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
@@ -2447,120 +2447,120 @@
         <v>27</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C22" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="E22" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="F22" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="G22" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="H22" s="5" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="I22" t="s">
-        <v>137</v>
+        <v>125</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="B23" t="s">
+        <v>100</v>
+      </c>
+      <c r="C23" t="s">
+        <v>102</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E23" t="s">
+        <v>103</v>
+      </c>
+      <c r="F23" t="s">
         <v>105</v>
       </c>
-      <c r="B23" t="s">
-        <v>108</v>
-      </c>
-      <c r="C23" t="s">
-        <v>110</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="E23" t="s">
-        <v>111</v>
-      </c>
-      <c r="F23" t="s">
-        <v>113</v>
-      </c>
       <c r="G23" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="H23" s="5" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="I23" t="s">
-        <v>138</v>
+        <v>126</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="B24" t="s">
+        <v>101</v>
+      </c>
+      <c r="C24" t="s">
+        <v>102</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E24" t="s">
+        <v>104</v>
+      </c>
+      <c r="F24" t="s">
         <v>106</v>
       </c>
-      <c r="B24" t="s">
-        <v>109</v>
-      </c>
-      <c r="C24" t="s">
-        <v>110</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="E24" t="s">
-        <v>112</v>
-      </c>
-      <c r="F24" t="s">
-        <v>114</v>
-      </c>
       <c r="G24" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="H24" s="5" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="I24" t="s">
-        <v>139</v>
+        <v>127</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="B25" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="C25" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="E25" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="F25" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="G25" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="H25" s="5" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="I25" s="7" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="6" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
     </row>
   </sheetData>

--- a/tests/Testing.xlsx
+++ b/tests/Testing.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4c7d7d98c037d19b/Level 6/Cloud/ACDT CW2 Updated/tests/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="112" documentId="8_{AB4D71AA-F82A-4017-8E7A-B8E1FF7AC13D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EB2213FE-3847-47D3-9F2D-26636208F9B4}"/>
+  <xr:revisionPtr revIDLastSave="114" documentId="8_{AB4D71AA-F82A-4017-8E7A-B8E1FF7AC13D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2475500D-28A0-4231-A0AC-6E663E320073}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{0FD93C22-EA38-4C55-8FBA-9A662F17215C}"/>
   </bookViews>
@@ -1496,10 +1496,10 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Picture 2">
+        <xdr:cNvPr id="2" name="Picture 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{58C4BEC0-A8AD-8244-2FDB-36038662FAB9}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2E5691BB-5CEC-769B-76F6-2ED2ADBE094E}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1526,6 +1526,10 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>

--- a/tests/Testing.xlsx
+++ b/tests/Testing.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4c7d7d98c037d19b/Level 6/Cloud/ACDT CW2 Updated/tests/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="114" documentId="8_{AB4D71AA-F82A-4017-8E7A-B8E1FF7AC13D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2475500D-28A0-4231-A0AC-6E663E320073}"/>
+  <xr:revisionPtr revIDLastSave="149" documentId="8_{AB4D71AA-F82A-4017-8E7A-B8E1FF7AC13D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CB9705F2-39DE-4EA8-9432-87AB52E9955E}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{0FD93C22-EA38-4C55-8FBA-9A662F17215C}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{0FD93C22-EA38-4C55-8FBA-9A662F17215C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="148">
   <si>
     <t>Test ID</t>
   </si>
@@ -406,9 +406,6 @@
     </r>
   </si>
   <si>
-    <t>Full output:</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <b/>
@@ -1358,13 +1355,40 @@
       </rPr>
       <t xml:space="preserve">   </t>
     </r>
+  </si>
+  <si>
+    <t>IT-01</t>
+  </si>
+  <si>
+    <t>End to end full run. Calling IntelX for real results</t>
+  </si>
+  <si>
+    <t>Integration</t>
+  </si>
+  <si>
+    <t>Full run through against live IntelX API and confirm outputs/logging</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Run `python -m alc_breach_screener` using existing email_list.csv and valid IntelX key </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Expected: output CSV + analyst summary + chart generated; </t>
+  </si>
+  <si>
+    <t>Full Test output:</t>
+  </si>
+  <si>
+    <t>Evidence: screenshot + demonstration video (screenshots below)</t>
+  </si>
+  <si>
+    <t>End to end full run through:</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1409,6 +1433,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -1442,7 +1473,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1462,6 +1493,10 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1489,8 +1524,8 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>3298167</xdr:colOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>1345542</xdr:colOff>
       <xdr:row>49</xdr:row>
       <xdr:rowOff>162533</xdr:rowOff>
     </xdr:to>
@@ -1521,6 +1556,155 @@
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>2811860</xdr:colOff>
+      <xdr:row>68</xdr:row>
+      <xdr:rowOff>19505</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4BB1EDFE-9D81-CAEC-E9D3-66AB3D49EE0A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="9906000"/>
+          <a:ext cx="14222810" cy="3258005"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>68</xdr:row>
+      <xdr:rowOff>142875</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>400340</xdr:colOff>
+      <xdr:row>85</xdr:row>
+      <xdr:rowOff>152853</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Picture 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{24A4D554-B3CA-9FAD-AB51-477A3B8D30AE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="13287375"/>
+          <a:ext cx="2076740" cy="3248478"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>428625</xdr:colOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>190499</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>96</xdr:row>
+      <xdr:rowOff>9524</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Picture 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9845CBEA-170E-58BF-D740-9CFADA2CBF65}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="2105025" y="13144499"/>
+          <a:ext cx="5343525" cy="5343525"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
@@ -1849,15 +2033,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A51DA75E-0BC6-4DA8-8300-BFD8F85011B5}">
-  <dimension ref="A1:I27"/>
+  <dimension ref="A1:I51"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="25.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="58.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="16.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="50.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="41.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="26.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="61.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="79.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="54.140625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.140625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="81.85546875" bestFit="1" customWidth="1"/>
   </cols>
@@ -1950,7 +2134,7 @@
         <v>45</v>
       </c>
       <c r="I4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
@@ -1979,7 +2163,7 @@
         <v>45</v>
       </c>
       <c r="I5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
@@ -2008,7 +2192,7 @@
         <v>45</v>
       </c>
       <c r="I6" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
@@ -2037,7 +2221,7 @@
         <v>45</v>
       </c>
       <c r="I7" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
@@ -2066,7 +2250,7 @@
         <v>45</v>
       </c>
       <c r="I8" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
@@ -2095,7 +2279,7 @@
         <v>45</v>
       </c>
       <c r="I9" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
@@ -2124,7 +2308,7 @@
         <v>45</v>
       </c>
       <c r="I10" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
@@ -2153,7 +2337,7 @@
         <v>45</v>
       </c>
       <c r="I11" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
@@ -2182,7 +2366,7 @@
         <v>45</v>
       </c>
       <c r="I12" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
@@ -2190,16 +2374,16 @@
         <v>18</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C13" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>44</v>
       </c>
       <c r="E13" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F13" t="s">
         <v>74</v>
@@ -2211,7 +2395,7 @@
         <v>45</v>
       </c>
       <c r="I13" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
@@ -2219,19 +2403,19 @@
         <v>19</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C14" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>44</v>
       </c>
       <c r="E14" t="s">
+        <v>129</v>
+      </c>
+      <c r="F14" t="s">
         <v>130</v>
-      </c>
-      <c r="F14" t="s">
-        <v>131</v>
       </c>
       <c r="G14" t="s">
         <v>83</v>
@@ -2240,7 +2424,7 @@
         <v>45</v>
       </c>
       <c r="I14" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
@@ -2248,10 +2432,10 @@
         <v>20</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C15" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>44</v>
@@ -2269,7 +2453,7 @@
         <v>45</v>
       </c>
       <c r="I15" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
@@ -2277,10 +2461,10 @@
         <v>21</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C16" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>44</v>
@@ -2298,7 +2482,7 @@
         <v>45</v>
       </c>
       <c r="I16" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
@@ -2327,7 +2511,7 @@
         <v>45</v>
       </c>
       <c r="I17" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
@@ -2356,7 +2540,7 @@
         <v>45</v>
       </c>
       <c r="I18" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
@@ -2385,7 +2569,7 @@
         <v>45</v>
       </c>
       <c r="I19" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
@@ -2414,7 +2598,7 @@
         <v>45</v>
       </c>
       <c r="I20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
@@ -2443,7 +2627,7 @@
         <v>45</v>
       </c>
       <c r="I21" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
@@ -2472,7 +2656,7 @@
         <v>45</v>
       </c>
       <c r="I22" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
@@ -2501,7 +2685,7 @@
         <v>45</v>
       </c>
       <c r="I23" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
@@ -2530,7 +2714,7 @@
         <v>45</v>
       </c>
       <c r="I24" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
@@ -2559,12 +2743,46 @@
         <v>45</v>
       </c>
       <c r="I25" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A26" s="8" t="s">
+        <v>139</v>
+      </c>
+      <c r="B26" t="s">
+        <v>140</v>
+      </c>
+      <c r="C26" t="s">
+        <v>89</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="E26" t="s">
+        <v>142</v>
+      </c>
+      <c r="F26" s="10" t="s">
+        <v>143</v>
+      </c>
+      <c r="G26" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="H26" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="I26" s="9" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="6" t="s">
-        <v>109</v>
+        <v>145</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A51" s="6" t="s">
+        <v>147</v>
       </c>
     </row>
   </sheetData>

--- a/tests/Testing.xlsx
+++ b/tests/Testing.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4c7d7d98c037d19b/Level 6/Cloud/ACDT CW2 Updated/tests/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="149" documentId="8_{AB4D71AA-F82A-4017-8E7A-B8E1FF7AC13D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CB9705F2-39DE-4EA8-9432-87AB52E9955E}"/>
+  <xr:revisionPtr revIDLastSave="153" documentId="8_{AB4D71AA-F82A-4017-8E7A-B8E1FF7AC13D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E4237589-773C-416A-9CCB-B4B680D9CA53}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{0FD93C22-EA38-4C55-8FBA-9A662F17215C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{0FD93C22-EA38-4C55-8FBA-9A662F17215C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -224,9 +224,6 @@
     <t>Ensure Retry-After header is honoured</t>
   </si>
   <si>
-    <t>Verify aggregation and top-N logic</t>
-  </si>
-  <si>
     <t>Verify summary CSV layout and content</t>
   </si>
   <si>
@@ -1382,6 +1379,9 @@
   </si>
   <si>
     <t>End to end full run through:</t>
+  </si>
+  <si>
+    <t>Verify analyst summary output</t>
   </si>
 </sst>
 </file>
@@ -1564,50 +1564,6 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>51</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>2811860</xdr:colOff>
-      <xdr:row>68</xdr:row>
-      <xdr:rowOff>19505</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Picture 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4BB1EDFE-9D81-CAEC-E9D3-66AB3D49EE0A}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="9906000"/>
-          <a:ext cx="14222810" cy="3258005"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
       <xdr:row>68</xdr:row>
       <xdr:rowOff>142875</xdr:rowOff>
     </xdr:from>
@@ -1631,7 +1587,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1675,7 +1631,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -1705,6 +1661,50 @@
             </a14:hiddenFill>
           </a:ext>
         </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>3392966</xdr:colOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>181426</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="Picture 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F105FBA3-873C-D68E-1459-D6F2DAAD9FE1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="9715500"/>
+          <a:ext cx="14803916" cy="3229426"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
@@ -2066,13 +2066,13 @@
         <v>6</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
       <c r="I1" s="6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
@@ -2096,16 +2096,16 @@
         <v>46</v>
       </c>
       <c r="F3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H3" s="5" t="s">
         <v>45</v>
       </c>
       <c r="I3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
@@ -2125,16 +2125,16 @@
         <v>47</v>
       </c>
       <c r="F4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H4" s="5" t="s">
         <v>45</v>
       </c>
       <c r="I4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
@@ -2145,7 +2145,7 @@
         <v>30</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>44</v>
@@ -2154,16 +2154,16 @@
         <v>48</v>
       </c>
       <c r="F5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H5" s="5" t="s">
         <v>45</v>
       </c>
       <c r="I5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
@@ -2174,7 +2174,7 @@
         <v>31</v>
       </c>
       <c r="C6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>44</v>
@@ -2183,16 +2183,16 @@
         <v>49</v>
       </c>
       <c r="F6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H6" s="5" t="s">
         <v>45</v>
       </c>
       <c r="I6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
@@ -2203,7 +2203,7 @@
         <v>32</v>
       </c>
       <c r="C7" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>44</v>
@@ -2212,16 +2212,16 @@
         <v>50</v>
       </c>
       <c r="F7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G7" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H7" s="5" t="s">
         <v>45</v>
       </c>
       <c r="I7" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
@@ -2232,7 +2232,7 @@
         <v>33</v>
       </c>
       <c r="C8" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>44</v>
@@ -2241,16 +2241,16 @@
         <v>51</v>
       </c>
       <c r="F8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H8" s="5" t="s">
         <v>45</v>
       </c>
       <c r="I8" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
@@ -2261,7 +2261,7 @@
         <v>34</v>
       </c>
       <c r="C9" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>44</v>
@@ -2270,16 +2270,16 @@
         <v>52</v>
       </c>
       <c r="F9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G9" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H9" s="5" t="s">
         <v>45</v>
       </c>
       <c r="I9" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
@@ -2290,7 +2290,7 @@
         <v>35</v>
       </c>
       <c r="C10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>44</v>
@@ -2299,16 +2299,16 @@
         <v>53</v>
       </c>
       <c r="F10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G10" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H10" s="5" t="s">
         <v>45</v>
       </c>
       <c r="I10" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
@@ -2319,7 +2319,7 @@
         <v>36</v>
       </c>
       <c r="C11" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>44</v>
@@ -2328,16 +2328,16 @@
         <v>54</v>
       </c>
       <c r="F11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G11" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H11" s="5" t="s">
         <v>45</v>
       </c>
       <c r="I11" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
@@ -2348,7 +2348,7 @@
         <v>37</v>
       </c>
       <c r="C12" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>44</v>
@@ -2357,16 +2357,16 @@
         <v>55</v>
       </c>
       <c r="F12" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G12" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H12" s="5" t="s">
         <v>45</v>
       </c>
       <c r="I12" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
@@ -2374,28 +2374,28 @@
         <v>18</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C13" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>44</v>
       </c>
       <c r="E13" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F13" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G13" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H13" s="5" t="s">
         <v>45</v>
       </c>
       <c r="I13" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
@@ -2403,28 +2403,28 @@
         <v>19</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C14" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>44</v>
       </c>
       <c r="E14" t="s">
+        <v>128</v>
+      </c>
+      <c r="F14" t="s">
         <v>129</v>
       </c>
-      <c r="F14" t="s">
-        <v>130</v>
-      </c>
       <c r="G14" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H14" s="5" t="s">
         <v>45</v>
       </c>
       <c r="I14" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
@@ -2432,10 +2432,10 @@
         <v>20</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C15" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>44</v>
@@ -2444,16 +2444,16 @@
         <v>56</v>
       </c>
       <c r="F15" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G15" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H15" s="5" t="s">
         <v>45</v>
       </c>
       <c r="I15" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
@@ -2461,10 +2461,10 @@
         <v>21</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C16" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>44</v>
@@ -2473,16 +2473,16 @@
         <v>57</v>
       </c>
       <c r="F16" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G16" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H16" s="5" t="s">
         <v>45</v>
       </c>
       <c r="I16" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
@@ -2502,16 +2502,16 @@
         <v>58</v>
       </c>
       <c r="F17" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G17" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H17" s="5" t="s">
         <v>45</v>
       </c>
       <c r="I17" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
@@ -2522,7 +2522,7 @@
         <v>39</v>
       </c>
       <c r="C18" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>44</v>
@@ -2531,16 +2531,16 @@
         <v>59</v>
       </c>
       <c r="F18" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G18" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H18" s="5" t="s">
         <v>45</v>
       </c>
       <c r="I18" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
@@ -2551,7 +2551,7 @@
         <v>40</v>
       </c>
       <c r="C19" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>44</v>
@@ -2560,16 +2560,16 @@
         <v>60</v>
       </c>
       <c r="F19" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G19" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H19" s="5" t="s">
         <v>45</v>
       </c>
       <c r="I19" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
@@ -2580,7 +2580,7 @@
         <v>41</v>
       </c>
       <c r="C20" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>44</v>
@@ -2589,16 +2589,16 @@
         <v>61</v>
       </c>
       <c r="F20" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G20" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H20" s="5" t="s">
         <v>45</v>
       </c>
       <c r="I20" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
@@ -2609,25 +2609,25 @@
         <v>42</v>
       </c>
       <c r="C21" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>44</v>
       </c>
       <c r="E21" t="s">
-        <v>62</v>
+        <v>147</v>
       </c>
       <c r="F21" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G21" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H21" s="5" t="s">
         <v>45</v>
       </c>
       <c r="I21" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
@@ -2638,151 +2638,151 @@
         <v>43</v>
       </c>
       <c r="C22" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D22" s="1" t="s">
         <v>44</v>
       </c>
       <c r="E22" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F22" t="s">
+        <v>81</v>
+      </c>
+      <c r="G22" t="s">
         <v>82</v>
-      </c>
-      <c r="G22" t="s">
-        <v>83</v>
       </c>
       <c r="H22" s="5" t="s">
         <v>45</v>
       </c>
       <c r="I22" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B23" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C23" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>44</v>
       </c>
       <c r="E23" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F23" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G23" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H23" s="5" t="s">
         <v>45</v>
       </c>
       <c r="I23" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" s="8" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B24" t="s">
+        <v>100</v>
+      </c>
+      <c r="C24" t="s">
         <v>101</v>
-      </c>
-      <c r="C24" t="s">
-        <v>102</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>44</v>
       </c>
       <c r="E24" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F24" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G24" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H24" s="5" t="s">
         <v>45</v>
       </c>
       <c r="I24" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="B25" t="s">
         <v>84</v>
       </c>
-      <c r="B25" t="s">
-        <v>85</v>
-      </c>
       <c r="C25" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>44</v>
       </c>
       <c r="E25" t="s">
+        <v>85</v>
+      </c>
+      <c r="F25" t="s">
         <v>86</v>
       </c>
-      <c r="F25" t="s">
-        <v>87</v>
-      </c>
       <c r="G25" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H25" s="5" t="s">
         <v>45</v>
       </c>
       <c r="I25" s="7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="B26" t="s">
         <v>139</v>
       </c>
-      <c r="B26" t="s">
+      <c r="C26" t="s">
+        <v>88</v>
+      </c>
+      <c r="D26" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="C26" t="s">
-        <v>89</v>
-      </c>
-      <c r="D26" s="1" t="s">
+      <c r="E26" t="s">
         <v>141</v>
       </c>
-      <c r="E26" t="s">
+      <c r="F26" s="10" t="s">
         <v>142</v>
       </c>
-      <c r="F26" s="10" t="s">
+      <c r="G26" s="9" t="s">
         <v>143</v>
-      </c>
-      <c r="G26" s="9" t="s">
-        <v>144</v>
       </c>
       <c r="H26" s="5" t="s">
         <v>45</v>
       </c>
       <c r="I26" s="9" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A51" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
   </sheetData>
